--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  15.09.2025 a 21.09.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  15.09.2025 a 21.09.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E07586B0-7B9B-4B19-90C0-C764EFA021F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F9DEE19-E069-411D-B5ED-4C1547BD6951}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15.09" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="85">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -171,13 +171,154 @@
 onforme CBE houve quebra de vigência de 274 dias e não houve sinis
 tro (Apólice cancelada em 31/12/24), conforme regra reduz nove cla
 sses de bônus, assim sendo o correto bônus 0.</t>
+  </si>
+  <si>
+    <t>LIMBO</t>
+  </si>
+  <si>
+    <t>ARBOREA COMERCIO E REPRESENTACOES LTDA ME CNPJ-  40490703000160</t>
+  </si>
+  <si>
+    <t>Demais Motivos</t>
+  </si>
+  <si>
+    <t> Chassi irregular, favor corrigir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELIANA DE OLIVEIRA NEVES                     </t>
+  </si>
+  <si>
+    <t>C
+onforme CBE houve quebra de vigência de 31 dias e não houve sinist
+ro (Apólice cancelada em 05/08/25), conforme regra mantem a classe
+de bônus, assim sendo o correto bônus  3</t>
+  </si>
+  <si>
+    <t>CASA DOS PARAFUSOS COMERCIO E SERVICOS LTDA M</t>
+  </si>
+  <si>
+    <t>falta de vistoria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE MARIA DA ROCHA                          </t>
+  </si>
+  <si>
+    <t>PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: HODOMETRO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO ROBERTO LEOPOLDINO                      </t>
+  </si>
+  <si>
+    <t>SILVA LANCHONETES CASAS DE CHA DE SUCOS E SIM</t>
+  </si>
+  <si>
+    <t>FRUSTRADA: CLIENTE NÃO CORRIGIU A FOTO INCORRETA - PRAZO EXPIRADO. FOTO INCORRETA: CHASSI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARIA APARECIDA RODRIGUES                    </t>
+  </si>
+  <si>
+    <t>A pedido segurado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO PEREIRA CHAVES                          </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 15.09.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LUIS ALFREDO COA ALFONZO                     </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JANAINA NABERCE BEZERRA                      </t>
+  </si>
+  <si>
+    <t>FRUSTRADA: CLIENTE NÃO CORRIGIU A FOTO INCORRETA - PRAZO EXPIRADO. FOTO INCORRETA - CHASSI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOAO LUCIO MARINO                            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">A A R DA SILVA ME                            </t>
+  </si>
+  <si>
+    <t>Bloqueio recusado devido ao parecer da vistoria prévia.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDERSON OGALLA CALI                         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE MILTON DOS SANTOS                       </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, a apólice foi renovada na
+congênere de origem. Portanto, peço a gentileza de encaminhar a d
+ocumentação abaixo para análise:Cópia da apólice congênere c
+om vigência de 2025 a 2026;Endosso de cancelamento emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCIA RIBEIRO MOTA                          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AQUI PROVEDOR BANDA LARGA LTDA ME            </t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Santander - Bônus correto deve ser {}, favor corrigir.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANIELE FROTA STEEL                          </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FC LIMA ATACADISTA HORTIFRUTI LTDA ME        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOIZES RODRIGUES PRESTES DE OLIVEIRA         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLIMPIO VALLI                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANILA LOPES DO NASCIMENTO FRAGA             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAIMUNDA MATIAS DOS SANTOS ABREU             </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARILIA DOS REIS SIQUEIRA                    </t>
+  </si>
+  <si>
+    <t>Conforme consulta na central de bônus, identificamos que a
+apólice consta ativa na congênere, para que possamos prosseguir
+coma liberação do bloqueio será necessário a apresentação do en
+dosso de cancelamento emitido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAMARA DE MEDEIROS ARAUJO                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IZAEL ANTONIO FERNANDES                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAUDY CAVALCANTI EL KHOURI SALAME MACHADO    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRUNO DE OLIVEIRA LUJAN                      </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALESANDRO PEREIRA DOS SANTOS JUNIOR          </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,8 +355,15 @@
       <color theme="1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -225,6 +373,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -491,10 +645,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -527,11 +677,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
@@ -543,16 +689,39 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal_Plan2_1" xfId="1" xr:uid="{69F13A52-20D9-46CA-8619-BC7A1BA09FD8}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -934,19 +1103,19 @@
       <c r="C2" s="27">
         <v>45915</v>
       </c>
-      <c r="D2" s="48">
+      <c r="D2" s="24">
         <v>134310407</v>
       </c>
-      <c r="E2" s="49">
+      <c r="E2" s="45">
         <v>3450074342</v>
       </c>
-      <c r="F2" s="46" t="s">
+      <c r="F2" s="12" t="s">
         <v>10</v>
       </c>
       <c r="G2" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="52" t="s">
+      <c r="H2" s="9" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="7">
@@ -963,13 +1132,13 @@
       <c r="C3" s="27">
         <v>45915</v>
       </c>
-      <c r="D3" s="48">
+      <c r="D3" s="24">
         <v>134323883</v>
       </c>
-      <c r="E3" s="50">
+      <c r="E3" s="46">
         <v>3450075101</v>
       </c>
-      <c r="F3" s="46" t="s">
+      <c r="F3" s="12" t="s">
         <v>13</v>
       </c>
       <c r="G3" s="20" t="s">
@@ -992,19 +1161,19 @@
       <c r="C4" s="27">
         <v>45915</v>
       </c>
-      <c r="D4" s="48">
+      <c r="D4" s="24">
         <v>134352986</v>
       </c>
-      <c r="E4" s="50">
+      <c r="E4" s="46">
         <v>3450076223</v>
       </c>
-      <c r="F4" s="46" t="s">
+      <c r="F4" s="12" t="s">
         <v>16</v>
       </c>
       <c r="G4" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="52" t="s">
+      <c r="H4" s="9" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="7">
@@ -1021,19 +1190,19 @@
       <c r="C5" s="27">
         <v>45915</v>
       </c>
-      <c r="D5" s="48">
+      <c r="D5" s="24">
         <v>134372332</v>
       </c>
-      <c r="E5" s="50">
+      <c r="E5" s="46">
         <v>3450077169</v>
       </c>
-      <c r="F5" s="46" t="s">
+      <c r="F5" s="12" t="s">
         <v>18</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I5" s="26">
@@ -1050,19 +1219,19 @@
       <c r="C6" s="27">
         <v>45915</v>
       </c>
-      <c r="D6" s="48">
+      <c r="D6" s="24">
         <v>134390711</v>
       </c>
-      <c r="E6" s="50">
+      <c r="E6" s="46">
         <v>3450078225</v>
       </c>
-      <c r="F6" s="46" t="s">
+      <c r="F6" s="12" t="s">
         <v>20</v>
       </c>
       <c r="G6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="53" t="s">
+      <c r="H6" s="21" t="s">
         <v>19</v>
       </c>
       <c r="I6" s="26">
@@ -1079,19 +1248,19 @@
       <c r="C7" s="27">
         <v>45915</v>
       </c>
-      <c r="D7" s="48">
+      <c r="D7" s="24">
         <v>134391642</v>
       </c>
-      <c r="E7" s="50">
+      <c r="E7" s="46">
         <v>3450078324</v>
       </c>
-      <c r="F7" s="46" t="s">
+      <c r="F7" s="12" t="s">
         <v>21</v>
       </c>
       <c r="G7" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="54" t="s">
+      <c r="H7" s="12" t="s">
         <v>19</v>
       </c>
       <c r="I7" s="26">
@@ -1108,13 +1277,13 @@
       <c r="C8" s="27">
         <v>45915</v>
       </c>
-      <c r="D8" s="48">
+      <c r="D8" s="24">
         <v>134311755</v>
       </c>
-      <c r="E8" s="50">
+      <c r="E8" s="46">
         <v>3450071780</v>
       </c>
-      <c r="F8" s="46" t="s">
+      <c r="F8" s="12" t="s">
         <v>22</v>
       </c>
       <c r="G8" s="25" t="s">
@@ -1137,19 +1306,19 @@
       <c r="C9" s="27">
         <v>45915</v>
       </c>
-      <c r="D9" s="48">
+      <c r="D9" s="24">
         <v>134376182</v>
       </c>
-      <c r="E9" s="50">
+      <c r="E9" s="46">
         <v>3450077323</v>
       </c>
-      <c r="F9" s="46" t="s">
+      <c r="F9" s="12" t="s">
         <v>25</v>
       </c>
       <c r="G9" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="55" t="s">
+      <c r="H9" s="15" t="s">
         <v>19</v>
       </c>
       <c r="I9" s="26">
@@ -1166,19 +1335,19 @@
       <c r="C10" s="27">
         <v>45915</v>
       </c>
-      <c r="D10" s="48">
+      <c r="D10" s="24">
         <v>134398093</v>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="46">
         <v>3450078511</v>
       </c>
-      <c r="F10" s="46" t="s">
+      <c r="F10" s="12" t="s">
         <v>26</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="52" t="s">
+      <c r="H10" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I10" s="26">
@@ -1195,19 +1364,19 @@
       <c r="C11" s="27">
         <v>45915</v>
       </c>
-      <c r="D11" s="48">
+      <c r="D11" s="24">
         <v>134442454</v>
       </c>
-      <c r="E11" s="50">
+      <c r="E11" s="46">
         <v>3450080392</v>
       </c>
-      <c r="F11" s="46" t="s">
+      <c r="F11" s="12" t="s">
         <v>29</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="52" t="s">
+      <c r="H11" s="9" t="s">
         <v>28</v>
       </c>
       <c r="I11" s="7">
@@ -1224,13 +1393,13 @@
       <c r="C12" s="27">
         <v>45915</v>
       </c>
-      <c r="D12" s="48">
+      <c r="D12" s="24">
         <v>134366614</v>
       </c>
-      <c r="E12" s="50">
+      <c r="E12" s="46">
         <v>3450076850</v>
       </c>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="12" t="s">
         <v>30</v>
       </c>
       <c r="G12" s="20" t="s">
@@ -1253,19 +1422,19 @@
       <c r="C13" s="27">
         <v>45915</v>
       </c>
-      <c r="D13" s="48">
+      <c r="D13" s="24">
         <v>134305172</v>
       </c>
-      <c r="E13" s="50">
+      <c r="E13" s="46">
         <v>3450073891</v>
       </c>
-      <c r="F13" s="46" t="s">
+      <c r="F13" s="12" t="s">
         <v>31</v>
       </c>
       <c r="G13" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="52" t="s">
+      <c r="H13" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I13" s="26">
@@ -1282,19 +1451,19 @@
       <c r="C14" s="27">
         <v>45915</v>
       </c>
-      <c r="D14" s="48">
+      <c r="D14" s="24">
         <v>134293168</v>
       </c>
-      <c r="E14" s="50">
+      <c r="E14" s="46">
         <v>3450073407</v>
       </c>
-      <c r="F14" s="46" t="s">
+      <c r="F14" s="12" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="52" t="s">
+      <c r="H14" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I14" s="26">
@@ -1311,19 +1480,19 @@
       <c r="C15" s="27">
         <v>45915</v>
       </c>
-      <c r="D15" s="48">
+      <c r="D15" s="24">
         <v>134357107</v>
       </c>
-      <c r="E15" s="50">
+      <c r="E15" s="46">
         <v>3450076465</v>
       </c>
-      <c r="F15" s="46" t="s">
+      <c r="F15" s="12" t="s">
         <v>32</v>
       </c>
       <c r="G15" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="52" t="s">
+      <c r="H15" s="9" t="s">
         <v>19</v>
       </c>
       <c r="I15" s="26">
@@ -1340,13 +1509,13 @@
       <c r="C16" s="27">
         <v>45915</v>
       </c>
-      <c r="D16" s="48">
+      <c r="D16" s="24">
         <v>134304782</v>
       </c>
-      <c r="E16" s="50">
+      <c r="E16" s="46">
         <v>3450073869</v>
       </c>
-      <c r="F16" s="46" t="s">
+      <c r="F16" s="12" t="s">
         <v>33</v>
       </c>
       <c r="G16" s="20" t="s">
@@ -1369,13 +1538,13 @@
       <c r="C17" s="27">
         <v>45915</v>
       </c>
-      <c r="D17" s="48">
+      <c r="D17" s="24">
         <v>134308199</v>
       </c>
-      <c r="E17" s="50">
+      <c r="E17" s="46">
         <v>3450074166</v>
       </c>
-      <c r="F17" s="46" t="s">
+      <c r="F17" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G17" s="20" t="s">
@@ -1398,13 +1567,13 @@
       <c r="C18" s="27">
         <v>45915</v>
       </c>
-      <c r="D18" s="48">
+      <c r="D18" s="24">
         <v>134310397</v>
       </c>
-      <c r="E18" s="50">
+      <c r="E18" s="46">
         <v>3450071450</v>
       </c>
-      <c r="F18" s="46" t="s">
+      <c r="F18" s="12" t="s">
         <v>35</v>
       </c>
       <c r="G18" s="20" t="s">
@@ -1427,13 +1596,13 @@
       <c r="C19" s="27">
         <v>45915</v>
       </c>
-      <c r="D19" s="48">
+      <c r="D19" s="24">
         <v>134311503</v>
       </c>
-      <c r="E19" s="50">
+      <c r="E19" s="46">
         <v>3450071581</v>
       </c>
-      <c r="F19" s="46" t="s">
+      <c r="F19" s="12" t="s">
         <v>36</v>
       </c>
       <c r="G19" s="20" t="s">
@@ -1456,19 +1625,19 @@
       <c r="C20" s="27">
         <v>45915</v>
       </c>
-      <c r="D20" s="48">
+      <c r="D20" s="24">
         <v>134357645</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="46">
         <v>3450076476</v>
       </c>
-      <c r="F20" s="46" t="s">
+      <c r="F20" s="12" t="s">
         <v>37</v>
       </c>
       <c r="G20" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H20" s="52" t="s">
+      <c r="H20" s="9" t="s">
         <v>38</v>
       </c>
       <c r="I20" s="26">
@@ -1485,19 +1654,19 @@
       <c r="C21" s="27">
         <v>45915</v>
       </c>
-      <c r="D21" s="48">
+      <c r="D21" s="24">
         <v>134221725</v>
       </c>
-      <c r="E21" s="50">
+      <c r="E21" s="46">
         <v>3450069557</v>
       </c>
-      <c r="F21" s="46" t="s">
+      <c r="F21" s="12" t="s">
         <v>39</v>
       </c>
       <c r="G21" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="H21" s="52" t="s">
+      <c r="H21" s="9" t="s">
         <v>41</v>
       </c>
       <c r="I21" s="26">
@@ -1508,9 +1677,9 @@
       <c r="A22" s="6"/>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
-      <c r="D22" s="47"/>
+      <c r="D22" s="44"/>
       <c r="E22" s="18"/>
-      <c r="F22" s="51"/>
+      <c r="F22" s="47"/>
       <c r="G22" s="20"/>
       <c r="H22" s="9"/>
       <c r="I22" s="26"/>
@@ -1894,7 +2063,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFA17127-7620-4DD9-9061-6C654E2EC5C2}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
@@ -1921,8 +2090,8 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
-        <v>4</v>
+      <c r="E1" s="3">
+        <v>3450075981</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>5</v>
@@ -1941,383 +2110,853 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="24"/>
-      <c r="E2" s="18"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="12"/>
+      <c r="B2" s="7">
+        <v>45915</v>
+      </c>
+      <c r="C2" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="49">
+        <v>3450080645</v>
+      </c>
+      <c r="F2" s="51" t="s">
+        <v>43</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>45</v>
+      </c>
       <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="9"/>
-      <c r="I3" s="26"/>
+      <c r="B3" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C3" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D3" s="24">
+        <v>134237714</v>
+      </c>
+      <c r="E3" s="18">
+        <v>3450070393</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" s="26">
+        <v>45908</v>
+      </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="B4" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C4" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D4" s="24">
+        <v>134317885</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450074749</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="53">
+        <v>45905</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="B5" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C5" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D5" s="24">
+        <v>134330051</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450075123</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="55" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" s="53">
+        <v>45905</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="20"/>
-      <c r="H6" s="21"/>
-      <c r="I6" s="26"/>
+      <c r="B6" s="7">
+        <v>45908</v>
+      </c>
+      <c r="C6" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D6" s="24">
+        <v>134343828</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450075915</v>
+      </c>
+      <c r="F6" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="53">
+        <v>45908</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="27"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="30"/>
-      <c r="I7" s="26"/>
+      <c r="B7" s="7">
+        <v>45909</v>
+      </c>
+      <c r="C7" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D7" s="24">
+        <v>134368293</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450077015</v>
+      </c>
+      <c r="F7" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="55" t="s">
+        <v>54</v>
+      </c>
+      <c r="I7" s="53">
+        <v>45909</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="24"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="25"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="26"/>
+      <c r="B8" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C8" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D8" s="24">
+        <v>134401023</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450077686</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="26">
+        <v>45916</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="24"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="20"/>
-      <c r="H9" s="15"/>
-      <c r="I9" s="26"/>
+      <c r="B9" s="7">
+        <v>45911</v>
+      </c>
+      <c r="C9" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D9" s="24">
+        <v>134404468</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450078820</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="G9" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="26">
+        <v>45915</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="26"/>
+      <c r="B10" s="7">
+        <v>45912</v>
+      </c>
+      <c r="C10" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D10" s="24">
+        <v>134416980</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450079501</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="26">
+        <v>45915</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="20"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="26"/>
+      <c r="B11" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C11" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D11" s="24">
+        <v>134399856</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450077543</v>
+      </c>
+      <c r="F11" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="26">
+        <v>45910</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="26"/>
+      <c r="B12" s="7">
+        <v>45916</v>
+      </c>
+      <c r="C12" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D12" s="24">
+        <v>134430990</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450080106</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="52" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="26">
+        <v>45915</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="26"/>
+      <c r="B13" s="7">
+        <v>45915</v>
+      </c>
+      <c r="C13" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D13" s="24">
+        <v>134453725</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450080843</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="52" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="26">
+        <v>45915</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="26"/>
+      <c r="B14" s="7">
+        <v>45908</v>
+      </c>
+      <c r="C14" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D14" s="24">
+        <v>134345149</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450075981</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="26">
+        <v>45916</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="26"/>
+      <c r="B15" s="7">
+        <v>45898</v>
+      </c>
+      <c r="C15" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D15" s="24">
+        <v>134201789</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450068567</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="52" t="s">
+        <v>67</v>
+      </c>
+      <c r="I15" s="26">
+        <v>45911</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="24"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="26"/>
+      <c r="B16" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C16" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D16" s="24">
+        <v>134270164</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450072208</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="26">
+        <v>45903</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="20"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="26"/>
+      <c r="B17" s="7">
+        <v>45909</v>
+      </c>
+      <c r="C17" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D17" s="24">
+        <v>134258382</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450071383</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H17" s="54" t="s">
+        <v>70</v>
+      </c>
+      <c r="I17" s="53">
+        <v>45909</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="26"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45903</v>
+      </c>
+      <c r="C18" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D18" s="24">
+        <v>134270225</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450072220</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" s="54" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="53">
+        <v>45905</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="27"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="20"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45908</v>
+      </c>
+      <c r="C19" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D19" s="24">
+        <v>134333955</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450075376</v>
+      </c>
+      <c r="F19" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H19" s="54" t="s">
+        <v>64</v>
+      </c>
+      <c r="I19" s="53">
+        <v>45908</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="27"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C20" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D20" s="24">
+        <v>134317031</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450074694</v>
+      </c>
+      <c r="F20" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="I20" s="53">
+        <v>45905</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="24"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="9"/>
-      <c r="I21" s="26"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C21" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D21" s="24">
+        <v>134317506</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450074716</v>
+      </c>
+      <c r="F21" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="I21" s="53">
+        <v>45905</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="20"/>
-      <c r="H22" s="9"/>
-      <c r="I22" s="26"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C22" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D22" s="24">
+        <v>134319091</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450074815</v>
+      </c>
+      <c r="F22" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="55" t="s">
+        <v>49</v>
+      </c>
+      <c r="I22" s="53">
+        <v>45905</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="24"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="20"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="26"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45906</v>
+      </c>
+      <c r="C23" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D23" s="24">
+        <v>134325899</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450075156</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" s="26">
+        <v>45906</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="24"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="9"/>
-      <c r="I24" s="26"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45902</v>
+      </c>
+      <c r="C24" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D24" s="24">
+        <v>134253201</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450071218</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H24" s="52" t="s">
+        <v>79</v>
+      </c>
+      <c r="I24" s="26">
+        <v>45908</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" s="6"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="24"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="9"/>
-      <c r="I25" s="26"/>
+      <c r="A25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="7">
+        <v>45915</v>
+      </c>
+      <c r="C25" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D25" s="24">
+        <v>134330424</v>
+      </c>
+      <c r="E25" s="18">
+        <v>3450074881</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H25" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I25" s="26">
+        <v>45915</v>
+      </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="24"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="26"/>
+      <c r="A26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="7">
+        <v>45908</v>
+      </c>
+      <c r="C26" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D26" s="24">
+        <v>134336419</v>
+      </c>
+      <c r="E26" s="18">
+        <v>3450075508</v>
+      </c>
+      <c r="F26" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H26" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I26" s="26">
+        <v>45908</v>
+      </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="6"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="24"/>
-      <c r="E27" s="18"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="20"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="26"/>
+      <c r="A27" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7">
+        <v>45908</v>
+      </c>
+      <c r="C27" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D27" s="24">
+        <v>134342955</v>
+      </c>
+      <c r="E27" s="18">
+        <v>3450075850</v>
+      </c>
+      <c r="F27" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H27" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I27" s="26">
+        <v>45908</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="18"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="9"/>
-      <c r="I28" s="26"/>
+      <c r="A28" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="7">
+        <v>45908</v>
+      </c>
+      <c r="C28" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D28" s="24">
+        <v>134344138</v>
+      </c>
+      <c r="E28" s="18">
+        <v>3450075948</v>
+      </c>
+      <c r="F28" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H28" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" s="26">
+        <v>45908</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="24"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="9"/>
-      <c r="I29" s="26"/>
+      <c r="A29" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B29" s="7">
+        <v>45908</v>
+      </c>
+      <c r="C29" s="27">
+        <v>45916</v>
+      </c>
+      <c r="D29" s="24">
+        <v>134346840</v>
+      </c>
+      <c r="E29" s="18">
+        <v>3450076113</v>
+      </c>
+      <c r="F29" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H29" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I29" s="26">
+        <v>45908</v>
+      </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="6"/>
       <c r="B30" s="7"/>
       <c r="C30" s="27"/>
-      <c r="D30" s="24"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="12"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="33"/>
       <c r="G30" s="20"/>
       <c r="H30" s="9"/>
       <c r="I30" s="26"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="6"/>
-      <c r="B31" s="7"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="24"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="20"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="7"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="6"/>
       <c r="H31" s="9"/>
       <c r="I31" s="26"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="6"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="24"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="20"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="7"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="6"/>
       <c r="H32" s="9"/>
       <c r="I32" s="26"/>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="6"/>
-      <c r="B33" s="7"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="24"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="20"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="7"/>
+      <c r="D33" s="8"/>
+      <c r="E33" s="8"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="6"/>
       <c r="H33" s="9"/>
       <c r="I33" s="26"/>
     </row>
@@ -2325,12 +2964,12 @@
       <c r="A34" s="6"/>
       <c r="B34" s="8"/>
       <c r="C34" s="7"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="15"/>
+      <c r="D34" s="8"/>
+      <c r="E34" s="8"/>
+      <c r="F34" s="9"/>
       <c r="G34" s="6"/>
       <c r="H34" s="9"/>
-      <c r="I34" s="26"/>
+      <c r="I34"/>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" s="6"/>
@@ -2341,7 +2980,7 @@
       <c r="F35" s="9"/>
       <c r="G35" s="6"/>
       <c r="H35" s="9"/>
-      <c r="I35" s="26"/>
+      <c r="I35"/>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" s="6"/>
@@ -2352,7 +2991,7 @@
       <c r="F36" s="9"/>
       <c r="G36" s="6"/>
       <c r="H36" s="9"/>
-      <c r="I36" s="26"/>
+      <c r="I36"/>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" s="6"/>
@@ -2530,50 +3169,20 @@
       <c r="H52" s="9"/>
       <c r="I52"/>
     </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="6"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="7"/>
-      <c r="D53" s="8"/>
-      <c r="E53" s="8"/>
-      <c r="F53" s="9"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="9"/>
-      <c r="I53"/>
-    </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="6"/>
-      <c r="B54" s="8"/>
-      <c r="C54" s="7"/>
-      <c r="D54" s="8"/>
-      <c r="E54" s="8"/>
-      <c r="F54" s="9"/>
-      <c r="G54" s="6"/>
-      <c r="H54" s="9"/>
-      <c r="I54"/>
-    </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-      <c r="I55"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="5">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="E2">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A33" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A30" xr:uid="{4D257AA8-3FDB-42B7-A450-B3788B0ABB12}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G38" xr:uid="{5FAA0C61-6912-46B8-8149-B719594B77CB}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2621,7 +3230,7 @@
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="30" t="s">
         <v>8</v>
       </c>
     </row>
@@ -3784,7 +4393,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="43" t="s">
+      <c r="H1" s="41" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -3800,8 +4409,8 @@
       <c r="D2" s="24"/>
       <c r="E2" s="18"/>
       <c r="F2" s="19"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="38"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="36"/>
       <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:9">
@@ -3813,8 +4422,8 @@
       <c r="D3" s="24"/>
       <c r="E3" s="18"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="41"/>
-      <c r="H3" s="38"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="36"/>
       <c r="I3" s="26"/>
     </row>
     <row r="4" spans="1:9">
@@ -3826,8 +4435,8 @@
       <c r="D4" s="24"/>
       <c r="E4" s="18"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="41"/>
-      <c r="H4" s="38"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="36"/>
       <c r="I4" s="26"/>
     </row>
     <row r="5" spans="1:9">
@@ -3839,8 +4448,8 @@
       <c r="D5" s="24"/>
       <c r="E5" s="18"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="37"/>
       <c r="I5" s="26"/>
     </row>
     <row r="6" spans="1:9">
@@ -3852,8 +4461,8 @@
       <c r="D6" s="24"/>
       <c r="E6" s="18"/>
       <c r="F6" s="19"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="38"/>
       <c r="I6" s="26"/>
     </row>
     <row r="7" spans="1:9">
@@ -3865,8 +4474,8 @@
       <c r="D7" s="24"/>
       <c r="E7" s="18"/>
       <c r="F7" s="19"/>
-      <c r="G7" s="44"/>
-      <c r="H7" s="40"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="38"/>
       <c r="I7" s="26"/>
     </row>
     <row r="8" spans="1:9">
@@ -3878,8 +4487,8 @@
       <c r="D8" s="24"/>
       <c r="E8" s="18"/>
       <c r="F8" s="19"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="40"/>
+      <c r="G8" s="43"/>
+      <c r="H8" s="38"/>
       <c r="I8" s="26"/>
     </row>
     <row r="9" spans="1:9">
@@ -3891,8 +4500,8 @@
       <c r="D9" s="24"/>
       <c r="E9" s="18"/>
       <c r="F9" s="19"/>
-      <c r="G9" s="45"/>
-      <c r="H9" s="38"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="36"/>
       <c r="I9" s="26"/>
     </row>
     <row r="10" spans="1:9">
@@ -3904,8 +4513,8 @@
       <c r="D10" s="24"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-      <c r="G10" s="45"/>
-      <c r="H10" s="38"/>
+      <c r="G10" s="43"/>
+      <c r="H10" s="36"/>
       <c r="I10" s="26"/>
     </row>
     <row r="11" spans="1:9">
@@ -3917,8 +4526,8 @@
       <c r="D11" s="24"/>
       <c r="E11" s="18"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="45"/>
-      <c r="H11" s="38"/>
+      <c r="G11" s="43"/>
+      <c r="H11" s="36"/>
       <c r="I11" s="26"/>
     </row>
     <row r="12" spans="1:9">
@@ -3930,8 +4539,8 @@
       <c r="D12" s="24"/>
       <c r="E12" s="18"/>
       <c r="F12" s="19"/>
-      <c r="G12" s="45"/>
-      <c r="H12" s="38"/>
+      <c r="G12" s="43"/>
+      <c r="H12" s="36"/>
       <c r="I12" s="26"/>
     </row>
     <row r="13" spans="1:9">
@@ -3943,8 +4552,8 @@
       <c r="D13" s="24"/>
       <c r="E13" s="18"/>
       <c r="F13" s="19"/>
-      <c r="G13" s="45"/>
-      <c r="H13" s="38"/>
+      <c r="G13" s="43"/>
+      <c r="H13" s="36"/>
       <c r="I13" s="26"/>
     </row>
     <row r="14" spans="1:9">
@@ -3956,8 +4565,8 @@
       <c r="D14" s="24"/>
       <c r="E14" s="18"/>
       <c r="F14" s="19"/>
-      <c r="G14" s="45"/>
-      <c r="H14" s="38"/>
+      <c r="G14" s="43"/>
+      <c r="H14" s="36"/>
       <c r="I14" s="26"/>
     </row>
     <row r="15" spans="1:9">
@@ -3969,8 +4578,8 @@
       <c r="D15" s="24"/>
       <c r="E15" s="18"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="45"/>
-      <c r="H15" s="38"/>
+      <c r="G15" s="43"/>
+      <c r="H15" s="36"/>
       <c r="I15" s="26"/>
     </row>
     <row r="16" spans="1:9">
@@ -3982,8 +4591,8 @@
       <c r="D16" s="24"/>
       <c r="E16" s="18"/>
       <c r="F16" s="12"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="38"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="36"/>
       <c r="I16" s="26"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1">
@@ -3995,8 +4604,8 @@
       <c r="D17" s="24"/>
       <c r="E17" s="18"/>
       <c r="F17" s="12"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="38"/>
+      <c r="G17" s="39"/>
+      <c r="H17" s="36"/>
       <c r="I17" s="26"/>
     </row>
     <row r="18" spans="1:9">
@@ -4008,8 +4617,8 @@
       <c r="D18" s="24"/>
       <c r="E18" s="18"/>
       <c r="F18" s="12"/>
-      <c r="G18" s="45"/>
-      <c r="H18" s="38"/>
+      <c r="G18" s="43"/>
+      <c r="H18" s="36"/>
       <c r="I18" s="26"/>
     </row>
     <row r="19" spans="1:9">
@@ -4017,9 +4626,9 @@
       <c r="B19" s="8"/>
       <c r="C19" s="7"/>
       <c r="D19" s="22"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="33"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="31"/>
       <c r="H19" s="9"/>
       <c r="I19" s="26"/>
     </row>
@@ -4030,7 +4639,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="15"/>
-      <c r="G20" s="33"/>
+      <c r="G20" s="31"/>
       <c r="H20" s="9"/>
       <c r="I20" s="26"/>
     </row>
@@ -4041,7 +4650,7 @@
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
       <c r="F21" s="9"/>
-      <c r="G21" s="33"/>
+      <c r="G21" s="31"/>
       <c r="H21" s="9"/>
       <c r="I21" s="26"/>
     </row>
@@ -4052,7 +4661,7 @@
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
       <c r="F22" s="9"/>
-      <c r="G22" s="33"/>
+      <c r="G22" s="31"/>
       <c r="H22" s="9"/>
       <c r="I22" s="26"/>
     </row>
@@ -4063,7 +4672,7 @@
       <c r="D23" s="8"/>
       <c r="E23" s="8"/>
       <c r="F23" s="9"/>
-      <c r="G23" s="33"/>
+      <c r="G23" s="31"/>
       <c r="H23" s="9"/>
       <c r="I23" s="26"/>
     </row>
@@ -4074,7 +4683,7 @@
       <c r="D24" s="8"/>
       <c r="E24" s="8"/>
       <c r="F24" s="9"/>
-      <c r="G24" s="33"/>
+      <c r="G24" s="31"/>
       <c r="H24" s="9"/>
       <c r="I24" s="26"/>
     </row>
@@ -4505,7 +5114,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="20"/>
       <c r="H3" s="9"/>
-      <c r="I3" s="37"/>
+      <c r="I3" s="35"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
@@ -4538,8 +5147,8 @@
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
       <c r="D6" s="22"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="35"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="33"/>
       <c r="G6" s="6"/>
       <c r="H6" s="9"/>
       <c r="I6" s="26"/>
@@ -5746,8 +6355,60 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="43" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="abf1b9912853fe4a934dbc2373304754">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d8d96f03b10d24171ef462918d18284e" ns1:_="" ns2:_="" ns3:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496579</_dlc_DocId>
+    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496579</Url>
+      <Description>QAFFA7D2F2TC-2102087286-496579</Description>
+    </_dlc_DocIdUrl>
+    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </DossierOwner>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ccca9d190a3c43e89f73773ee806c8b5>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ia4b831ccad64069ad2e0cbd870e9b8a>
+    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
+    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
+      <UserInfo>
+        <DisplayName/>
+        <AccountId xsi:nil="true"/>
+        <AccountType/>
+      </UserInfo>
+    </alteradopor>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
     <xsd:import namespace="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea"/>
     <xsd:import namespace="ea6c6725-5210-4d6a-93cc-4cf85111ac5e"/>
@@ -5785,6 +6446,7 @@
                 <xsd:element ref="ns3:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns3:_Flow_SignoffStatus" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -6017,6 +6679,11 @@
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="39" nillable="true" ma:displayName="Location" ma:description="" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
     <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
@@ -6117,64 +6784,12 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496579</_dlc_DocId>
-    <_dlc_DocIdUrl xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Url>https://allianzms.sharepoint.com/teams/BR0010-4356589/_layouts/15/DocIdRedir.aspx?ID=QAFFA7D2F2TC-2102087286-496579</Url>
-      <Description>QAFFA7D2F2TC-2102087286-496579</Description>
-    </_dlc_DocIdUrl>
-    <DossierOwner xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </DossierOwner>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ccca9d190a3c43e89f73773ee806c8b5 xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ccca9d190a3c43e89f73773ee806c8b5>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <ContractDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <MailPreviewData xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <_Flow_SignoffStatus xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ContractExpirationDate xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <DossierStatus xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <ia4b831ccad64069ad2e0cbd870e9b8a xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ia4b831ccad64069ad2e0cbd870e9b8a>
-    <TaxCatchAll xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xsi:nil="true"/>
-    <alteradopor xmlns="ea6c6725-5210-4d6a-93cc-4cf85111ac5e">
-      <UserInfo>
-        <DisplayName/>
-        <AccountId xsi:nil="true"/>
-        <AccountType/>
-      </UserInfo>
-    </alteradopor>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{098F1F3C-7054-44DA-97C1-1FA0AD811FFC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6182,5 +6797,5 @@
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F01CFAB-0890-48C6-9F7B-BC4BA038F67A}"/>
 </file>
--- a/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  15.09.2025 a 21.09.2025.xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/Arquivos/Relatório de Recusas  15.09.2025 a 21.09.2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://allianzms.sharepoint.com/teams/BR0010-4356589/Shared Documents/BACK-OFFICE SME/Santander/2025/Relatório de Recusas/05. Maio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{47E504C1-8165-4DC5-AD78-60704C8E24E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F34906F-FACF-4E4F-B954-E85CCFC146BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19530" windowHeight="9780" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="15.09" sheetId="2" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="134">
   <si>
     <t>SEGURADORA</t>
   </si>
@@ -384,6 +384,88 @@
   </si>
   <si>
     <t xml:space="preserve">FRUSTRADO, PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: PAINEL COM A MOTO LIGADA </t>
+  </si>
+  <si>
+    <t>ANTONIO APARECIDO DOS SANTOS CPF-32043013890</t>
+  </si>
+  <si>
+    <t>Chassi irregular, favor corrigir</t>
+  </si>
+  <si>
+    <t>CELIA MARIA SANDOVAL DE LIMA CASTRO CPF- 32947094808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREA ROMERO DE SOUZA                       </t>
+  </si>
+  <si>
+    <t>C
+onforme regra de apólices canceladas por vigência de curto prazo,
+houve quebra de vigência de 338 dias, portanto deve-se reduzir 10
+classes de bônus, assim sendo o correto bônus 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALECSSANDRE RODRIGUES TANURI                 </t>
+  </si>
+  <si>
+    <t>NUP Cancelamento 17.09.2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALEIDE SANDRA SIQUEIRA                       </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EDNA CRISTINA SPIGALI                        </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DANILO MARCOLINO NEVES                       </t>
+  </si>
+  <si>
+    <t>PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: hodômetro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JHONATAN HERCULANO MAZALI                    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAROLINE CRISTINE GREGORIO RUBINATO          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARELISE DE TOLEDO QUEIROZ ALVARENGA         </t>
+  </si>
+  <si>
+    <t>Santander - Veículo informado é diferente do calculado.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROSELI SAMPAIO DE SOUZA FREITAS              </t>
+  </si>
+  <si>
+    <t xml:space="preserve">JOSE SALVADOR                                </t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRASIL DISTRIBUIDORA UTILIDADES E PESCA LTDA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANDREIA LORENCETTI CARLOS                    </t>
+  </si>
+  <si>
+    <t>A análise para aceitação
+desta proposta está condicionada a envio de inspeção veicula</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FILLKVEST JEANS LTDA ME                      </t>
+  </si>
+  <si>
+    <t>PRAZO PARA REENVIO EXPIRADO. FOTOS NÃO CORRIGIDAS: Painel com carro ligado, Porta malas aberto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WAGNER HENRIQUE GRACIANO DE OLIVEIRA         </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADAILSON PEREIRA DE OLIVEIRA                 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">PAULO ROBERTO HONORIO DE MELO FILHO          </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SILVIO ADRIANO DA SILVA ACOUGUE ME           </t>
   </si>
 </sst>
 </file>
@@ -642,7 +724,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -772,25 +854,22 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3325,19 +3404,19 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="61">
+      <c r="B2" s="53">
         <v>45909</v>
       </c>
       <c r="C2" s="27">
         <v>45917</v>
       </c>
-      <c r="D2" s="58">
+      <c r="D2" s="24">
         <v>134368647</v>
       </c>
       <c r="E2" s="18">
         <v>3450077059</v>
       </c>
-      <c r="F2" s="54" t="s">
+      <c r="F2" s="12" t="s">
         <v>85</v>
       </c>
       <c r="G2" s="20" t="s">
@@ -3354,19 +3433,19 @@
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="61">
+      <c r="B3" s="53">
         <v>45911</v>
       </c>
       <c r="C3" s="27">
         <v>45917</v>
       </c>
-      <c r="D3" s="58">
+      <c r="D3" s="24">
         <v>134410569</v>
       </c>
       <c r="E3" s="18">
         <v>3450079281</v>
       </c>
-      <c r="F3" s="54" t="s">
+      <c r="F3" s="12" t="s">
         <v>86</v>
       </c>
       <c r="G3" s="25" t="s">
@@ -3383,19 +3462,19 @@
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="61">
+      <c r="B4" s="53">
         <v>45912</v>
       </c>
       <c r="C4" s="27">
         <v>45917</v>
       </c>
-      <c r="D4" s="58">
+      <c r="D4" s="24">
         <v>134416448</v>
       </c>
       <c r="E4" s="18">
         <v>3450079479</v>
       </c>
-      <c r="F4" s="54" t="s">
+      <c r="F4" s="12" t="s">
         <v>88</v>
       </c>
       <c r="G4" s="25" t="s">
@@ -3412,25 +3491,25 @@
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="61">
+      <c r="B5" s="53">
         <v>45912</v>
       </c>
       <c r="C5" s="27">
         <v>45917</v>
       </c>
-      <c r="D5" s="60">
+      <c r="D5" s="28">
         <v>134416827</v>
       </c>
       <c r="E5" s="18">
         <v>3450079480</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="19" t="s">
         <v>90</v>
       </c>
       <c r="G5" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H5" s="56" t="s">
+      <c r="H5" s="15" t="s">
         <v>91</v>
       </c>
       <c r="I5" s="26">
@@ -3441,19 +3520,19 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="61">
+      <c r="B6" s="53">
         <v>45929</v>
       </c>
       <c r="C6" s="27">
         <v>45917</v>
       </c>
-      <c r="D6" s="58">
+      <c r="D6" s="24">
         <v>134443930</v>
       </c>
       <c r="E6" s="18">
         <v>3450080414</v>
       </c>
-      <c r="F6" s="54" t="s">
+      <c r="F6" s="12" t="s">
         <v>92</v>
       </c>
       <c r="G6" s="20" t="s">
@@ -3470,25 +3549,25 @@
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="61">
+      <c r="B7" s="53">
         <v>45916</v>
       </c>
       <c r="C7" s="27">
         <v>45917</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="24">
         <v>134472466</v>
       </c>
       <c r="E7" s="18">
         <v>3450081569</v>
       </c>
-      <c r="F7" s="54" t="s">
+      <c r="F7" s="12" t="s">
         <v>93</v>
       </c>
       <c r="G7" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="57" t="s">
+      <c r="H7" s="9" t="s">
         <v>64</v>
       </c>
       <c r="I7" s="26">
@@ -3499,25 +3578,25 @@
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="61">
+      <c r="B8" s="53">
         <v>45903</v>
       </c>
       <c r="C8" s="27">
         <v>45917</v>
       </c>
-      <c r="D8" s="58">
+      <c r="D8" s="24">
         <v>134281070</v>
       </c>
       <c r="E8" s="18">
         <v>3450072703</v>
       </c>
-      <c r="F8" s="54" t="s">
+      <c r="F8" s="12" t="s">
         <v>94</v>
       </c>
       <c r="G8" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="H8" s="62" t="s">
+      <c r="H8" s="54" t="s">
         <v>24</v>
       </c>
       <c r="I8" s="26">
@@ -3528,19 +3607,19 @@
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="61">
+      <c r="B9" s="53">
         <v>45904</v>
       </c>
       <c r="C9" s="27">
         <v>45917</v>
       </c>
-      <c r="D9" s="58">
+      <c r="D9" s="24">
         <v>134287555</v>
       </c>
       <c r="E9" s="18">
         <v>3450072912</v>
       </c>
-      <c r="F9" s="54" t="s">
+      <c r="F9" s="12" t="s">
         <v>95</v>
       </c>
       <c r="G9" s="23" t="s">
@@ -3557,25 +3636,25 @@
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="61">
+      <c r="B10" s="53">
         <v>45904</v>
       </c>
       <c r="C10" s="27">
         <v>45917</v>
       </c>
-      <c r="D10" s="58">
+      <c r="D10" s="24">
         <v>134288001</v>
       </c>
       <c r="E10" s="18">
         <v>3450073000</v>
       </c>
-      <c r="F10" s="54" t="s">
+      <c r="F10" s="12" t="s">
         <v>96</v>
       </c>
       <c r="G10" s="20" t="s">
         <v>97</v>
       </c>
-      <c r="H10" s="57" t="s">
+      <c r="H10" s="9" t="s">
         <v>98</v>
       </c>
       <c r="I10" s="26">
@@ -3586,25 +3665,25 @@
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="61">
+      <c r="B11" s="53">
         <v>45935</v>
       </c>
       <c r="C11" s="27">
         <v>45917</v>
       </c>
-      <c r="D11" s="58">
+      <c r="D11" s="24">
         <v>134308384</v>
       </c>
       <c r="E11" s="18">
         <v>3450074210</v>
       </c>
-      <c r="F11" s="54" t="s">
+      <c r="F11" s="12" t="s">
         <v>99</v>
       </c>
       <c r="G11" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="H11" s="57" t="s">
+      <c r="H11" s="9" t="s">
         <v>79</v>
       </c>
       <c r="I11" s="26">
@@ -3615,25 +3694,25 @@
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="61">
+      <c r="B12" s="53">
         <v>45909</v>
       </c>
       <c r="C12" s="27">
         <v>45917</v>
       </c>
-      <c r="D12" s="58">
+      <c r="D12" s="24">
         <v>134353962</v>
       </c>
       <c r="E12" s="18">
         <v>3450076289</v>
       </c>
-      <c r="F12" s="54" t="s">
+      <c r="F12" s="12" t="s">
         <v>100</v>
       </c>
       <c r="G12" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H12" s="62" t="s">
+      <c r="H12" s="54" t="s">
         <v>101</v>
       </c>
       <c r="I12" s="26">
@@ -3644,19 +3723,19 @@
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="61">
+      <c r="B13" s="53">
         <v>45923</v>
       </c>
       <c r="C13" s="27">
         <v>45917</v>
       </c>
-      <c r="D13" s="58">
+      <c r="D13" s="24">
         <v>134354255</v>
       </c>
       <c r="E13" s="18">
         <v>3450076058</v>
       </c>
-      <c r="F13" s="54" t="s">
+      <c r="F13" s="12" t="s">
         <v>102</v>
       </c>
       <c r="G13" s="20" t="s">
@@ -3679,13 +3758,13 @@
       <c r="C14" s="27">
         <v>45917</v>
       </c>
-      <c r="D14" s="58">
+      <c r="D14" s="24">
         <v>134357895</v>
       </c>
       <c r="E14" s="18">
         <v>3450076498</v>
       </c>
-      <c r="F14" s="54" t="s">
+      <c r="F14" s="12" t="s">
         <v>103</v>
       </c>
       <c r="G14" s="20" t="s">
@@ -3708,13 +3787,13 @@
       <c r="C15" s="27">
         <v>45917</v>
       </c>
-      <c r="D15" s="58">
+      <c r="D15" s="24">
         <v>134367117</v>
       </c>
       <c r="E15" s="18">
         <v>3450076883</v>
       </c>
-      <c r="F15" s="54" t="s">
+      <c r="F15" s="12" t="s">
         <v>104</v>
       </c>
       <c r="G15" s="23" t="s">
@@ -3737,13 +3816,13 @@
       <c r="C16" s="27">
         <v>45917</v>
       </c>
-      <c r="D16" s="58">
+      <c r="D16" s="24">
         <v>134367628</v>
       </c>
       <c r="E16" s="18">
         <v>3450076938</v>
       </c>
-      <c r="F16" s="54" t="s">
+      <c r="F16" s="12" t="s">
         <v>105</v>
       </c>
       <c r="G16" s="20" t="s">
@@ -3766,19 +3845,19 @@
       <c r="C17" s="27">
         <v>45917</v>
       </c>
-      <c r="D17" s="58">
+      <c r="D17" s="24">
         <v>134407560</v>
       </c>
       <c r="E17" s="18">
         <v>3450079116</v>
       </c>
-      <c r="F17" s="54" t="s">
+      <c r="F17" s="12" t="s">
         <v>106</v>
       </c>
       <c r="G17" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="H17" s="57" t="s">
+      <c r="H17" s="9" t="s">
         <v>107</v>
       </c>
       <c r="I17" s="26">
@@ -3791,7 +3870,7 @@
       <c r="C18" s="27"/>
       <c r="D18" s="44"/>
       <c r="E18" s="50"/>
-      <c r="F18" s="55"/>
+      <c r="F18" s="33"/>
       <c r="G18" s="20"/>
       <c r="H18" s="9"/>
     </row>
@@ -3801,7 +3880,7 @@
       <c r="C19" s="27"/>
       <c r="D19" s="24"/>
       <c r="E19" s="18"/>
-      <c r="F19" s="53"/>
+      <c r="F19" s="12"/>
       <c r="G19" s="20"/>
       <c r="H19" s="9"/>
     </row>
@@ -3811,7 +3890,7 @@
       <c r="C20" s="27"/>
       <c r="D20" s="24"/>
       <c r="E20" s="18"/>
-      <c r="F20" s="53"/>
+      <c r="F20" s="12"/>
       <c r="G20" s="20"/>
       <c r="H20" s="9"/>
     </row>
@@ -3821,7 +3900,7 @@
       <c r="C21" s="27"/>
       <c r="D21" s="24"/>
       <c r="E21" s="18"/>
-      <c r="F21" s="53"/>
+      <c r="F21" s="12"/>
       <c r="G21" s="23"/>
       <c r="H21" s="9"/>
     </row>
@@ -3831,7 +3910,7 @@
       <c r="C22" s="27"/>
       <c r="D22" s="24"/>
       <c r="E22" s="18"/>
-      <c r="F22" s="53"/>
+      <c r="F22" s="12"/>
       <c r="G22" s="20"/>
       <c r="H22" s="9"/>
     </row>
@@ -3841,7 +3920,7 @@
       <c r="C23" s="27"/>
       <c r="D23" s="24"/>
       <c r="E23" s="18"/>
-      <c r="F23" s="53"/>
+      <c r="F23" s="12"/>
       <c r="G23" s="20"/>
       <c r="H23" s="9"/>
     </row>
@@ -3851,7 +3930,7 @@
       <c r="C24" s="27"/>
       <c r="D24" s="24"/>
       <c r="E24" s="18"/>
-      <c r="F24" s="53"/>
+      <c r="F24" s="12"/>
       <c r="G24" s="20"/>
       <c r="H24" s="9"/>
     </row>
@@ -3861,7 +3940,7 @@
       <c r="C25" s="27"/>
       <c r="D25" s="24"/>
       <c r="E25" s="18"/>
-      <c r="F25" s="53"/>
+      <c r="F25" s="12"/>
       <c r="G25" s="20"/>
       <c r="H25" s="9"/>
     </row>
@@ -3871,7 +3950,7 @@
       <c r="C26" s="27"/>
       <c r="D26" s="24"/>
       <c r="E26" s="18"/>
-      <c r="F26" s="53"/>
+      <c r="F26" s="12"/>
       <c r="G26" s="23"/>
       <c r="H26" s="9"/>
     </row>
@@ -3881,7 +3960,7 @@
       <c r="C27" s="27"/>
       <c r="D27" s="24"/>
       <c r="E27" s="18"/>
-      <c r="F27" s="53"/>
+      <c r="F27" s="12"/>
       <c r="G27" s="23"/>
       <c r="H27" s="9"/>
     </row>
@@ -3891,7 +3970,7 @@
       <c r="C28" s="27"/>
       <c r="D28" s="24"/>
       <c r="E28" s="18"/>
-      <c r="F28" s="53"/>
+      <c r="F28" s="12"/>
       <c r="G28" s="23"/>
       <c r="H28" s="9"/>
     </row>
@@ -3901,7 +3980,7 @@
       <c r="C29" s="27"/>
       <c r="D29" s="24"/>
       <c r="E29" s="18"/>
-      <c r="F29" s="53"/>
+      <c r="F29" s="12"/>
       <c r="G29" s="23"/>
       <c r="H29" s="9"/>
     </row>
@@ -4038,14 +4117,14 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF216D7-F2B3-4C54-A7B9-7048B06C2C75}">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="26" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" customWidth="1"/>
+    <col min="4" max="4" width="22.7109375" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="36.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="36.5703125" bestFit="1" customWidth="1"/>
@@ -4085,288 +4164,675 @@
       <c r="A2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="9"/>
+      <c r="B2" s="7">
+        <v>45917</v>
+      </c>
+      <c r="C2" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="E2" s="57">
+        <v>3450082834</v>
+      </c>
+      <c r="F2" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H2" s="59" t="s">
+        <v>109</v>
+      </c>
       <c r="I2" s="26"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="9"/>
+      <c r="B3" s="7">
+        <v>45917</v>
+      </c>
+      <c r="C3" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D3" s="56" t="s">
+        <v>42</v>
+      </c>
+      <c r="E3" s="57">
+        <v>3450082295</v>
+      </c>
+      <c r="F3" s="51" t="s">
+        <v>110</v>
+      </c>
+      <c r="G3" s="29" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="59" t="s">
+        <v>109</v>
+      </c>
       <c r="I3" s="26"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="9"/>
-      <c r="I4" s="26"/>
+      <c r="B4" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C4" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D4" s="57">
+        <v>134306265</v>
+      </c>
+      <c r="E4" s="18">
+        <v>3450074012</v>
+      </c>
+      <c r="F4" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="G4" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="H4" s="58" t="s">
+        <v>112</v>
+      </c>
+      <c r="I4" s="26">
+        <v>45910</v>
+      </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="8"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="26"/>
+      <c r="B5" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C5" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D5" s="57">
+        <v>134391349</v>
+      </c>
+      <c r="E5" s="18">
+        <v>3450078269</v>
+      </c>
+      <c r="F5" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I5" s="26">
+        <v>45917</v>
+      </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="26"/>
+      <c r="B6" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C6" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D6" s="57">
+        <v>134387165</v>
+      </c>
+      <c r="E6" s="18">
+        <v>3450077983</v>
+      </c>
+      <c r="F6" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="G6" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="58" t="s">
+        <v>49</v>
+      </c>
+      <c r="I6" s="26">
+        <v>45910</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="9"/>
-      <c r="I7" s="26"/>
+      <c r="B7" s="7">
+        <v>45911</v>
+      </c>
+      <c r="C7" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D7" s="57">
+        <v>134406609</v>
+      </c>
+      <c r="E7" s="18">
+        <v>3450079039</v>
+      </c>
+      <c r="F7" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I7" s="26">
+        <v>45917</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="9"/>
-      <c r="I8" s="26"/>
+      <c r="B8" s="7">
+        <v>45926</v>
+      </c>
+      <c r="C8" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D8" s="57">
+        <v>134421442</v>
+      </c>
+      <c r="E8" s="18">
+        <v>3450079710</v>
+      </c>
+      <c r="F8" s="55" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I8" s="26">
+        <v>45917</v>
+      </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="26"/>
+      <c r="B9" s="7">
+        <v>45912</v>
+      </c>
+      <c r="C9" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D9" s="57">
+        <v>134419744</v>
+      </c>
+      <c r="E9" s="18">
+        <v>3450079590</v>
+      </c>
+      <c r="F9" s="55" t="s">
+        <v>117</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>118</v>
+      </c>
+      <c r="I9" s="26">
+        <v>45912</v>
+      </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="26"/>
+      <c r="B10" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C10" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D10" s="57">
+        <v>134380281</v>
+      </c>
+      <c r="E10" s="18">
+        <v>3450077631</v>
+      </c>
+      <c r="F10" s="55" t="s">
+        <v>119</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I10" s="26">
+        <v>45910</v>
+      </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="26"/>
+      <c r="B11" s="7">
+        <v>45916</v>
+      </c>
+      <c r="C11" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D11" s="57">
+        <v>134484052</v>
+      </c>
+      <c r="E11" s="18">
+        <v>3450082097</v>
+      </c>
+      <c r="F11" s="55" t="s">
+        <v>120</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="I11" s="26">
+        <v>45916</v>
+      </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="26"/>
+      <c r="B12" s="7">
+        <v>45917</v>
+      </c>
+      <c r="C12" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D12" s="57">
+        <v>134494307</v>
+      </c>
+      <c r="E12" s="18">
+        <v>3450082460</v>
+      </c>
+      <c r="F12" s="55" t="s">
+        <v>26</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="I12" s="26">
+        <v>45917</v>
+      </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="26"/>
+      <c r="B13" s="7">
+        <v>45917</v>
+      </c>
+      <c r="C13" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D13" s="57">
+        <v>134490512</v>
+      </c>
+      <c r="E13" s="18">
+        <v>3450082306</v>
+      </c>
+      <c r="F13" s="55" t="s">
+        <v>63</v>
+      </c>
+      <c r="G13" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="26">
+        <v>45917</v>
+      </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="8"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="26"/>
+      <c r="B14" s="7">
+        <v>45908</v>
+      </c>
+      <c r="C14" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D14" s="57">
+        <v>134342644</v>
+      </c>
+      <c r="E14" s="18">
+        <v>3450075827</v>
+      </c>
+      <c r="F14" s="55" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="26">
+        <v>45910</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="26"/>
+      <c r="B15" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C15" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D15" s="57">
+        <v>134321378</v>
+      </c>
+      <c r="E15" s="18">
+        <v>3450074947</v>
+      </c>
+      <c r="F15" s="55" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="58" t="s">
+        <v>122</v>
+      </c>
+      <c r="I15" s="26">
+        <v>45905</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="6"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="26"/>
+      <c r="A16" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C16" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D16" s="57">
+        <v>134318246</v>
+      </c>
+      <c r="E16" s="18">
+        <v>3450074771</v>
+      </c>
+      <c r="F16" s="55" t="s">
+        <v>123</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I16" s="26">
+        <v>45917</v>
+      </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="6"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="26"/>
+      <c r="A17" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C17" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D17" s="57">
+        <v>134379626</v>
+      </c>
+      <c r="E17" s="18">
+        <v>3450077521</v>
+      </c>
+      <c r="F17" s="55" t="s">
+        <v>124</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I17" s="26">
+        <v>45917</v>
+      </c>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="26"/>
+      <c r="A18" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="7">
+        <v>45915</v>
+      </c>
+      <c r="C18" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D18" s="57">
+        <v>134458947</v>
+      </c>
+      <c r="E18" s="18">
+        <v>3450081030</v>
+      </c>
+      <c r="F18" s="55" t="s">
+        <v>125</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" s="26">
+        <v>45917</v>
+      </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="6"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="26"/>
+      <c r="A19" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="7">
+        <v>45905</v>
+      </c>
+      <c r="C19" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D19" s="57">
+        <v>134306197</v>
+      </c>
+      <c r="E19" s="18">
+        <v>3450073990</v>
+      </c>
+      <c r="F19" s="55" t="s">
+        <v>126</v>
+      </c>
+      <c r="G19" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="H19" s="58" t="s">
+        <v>127</v>
+      </c>
+      <c r="I19" s="26">
+        <v>45910</v>
+      </c>
     </row>
     <row r="20" spans="1:9">
-      <c r="A20" s="6"/>
-      <c r="B20" s="8"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="9"/>
-      <c r="I20" s="26"/>
+      <c r="A20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C20" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D20" s="57">
+        <v>134378477</v>
+      </c>
+      <c r="E20" s="18">
+        <v>3450077411</v>
+      </c>
+      <c r="F20" s="55" t="s">
+        <v>128</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="58" t="s">
+        <v>129</v>
+      </c>
+      <c r="I20" s="26">
+        <v>45910</v>
+      </c>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="6"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="8"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="6"/>
-      <c r="H21" s="9"/>
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C21" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D21" s="57">
+        <v>134376163</v>
+      </c>
+      <c r="E21" s="18">
+        <v>3450077312</v>
+      </c>
+      <c r="F21" s="55" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H21" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="I21" s="26">
+        <v>45910</v>
+      </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="6"/>
-      <c r="B22" s="8"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="8"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="9"/>
+      <c r="A22" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C22" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D22" s="57">
+        <v>134377562</v>
+      </c>
+      <c r="E22" s="18">
+        <v>3450077389</v>
+      </c>
+      <c r="F22" s="55" t="s">
+        <v>131</v>
+      </c>
+      <c r="G22" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="H22" s="58" t="s">
+        <v>64</v>
+      </c>
+      <c r="I22" s="26">
+        <v>45910</v>
+      </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="6"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="6"/>
-      <c r="H23" s="9"/>
+      <c r="A23" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C23" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D23" s="57">
+        <v>134382820</v>
+      </c>
+      <c r="E23" s="18">
+        <v>3450077796</v>
+      </c>
+      <c r="F23" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I23" s="26">
+        <v>45910</v>
+      </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="6"/>
-      <c r="B24" s="8"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="9"/>
+      <c r="A24" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="7">
+        <v>45910</v>
+      </c>
+      <c r="C24" s="7">
+        <v>45918</v>
+      </c>
+      <c r="D24" s="57">
+        <v>134384068</v>
+      </c>
+      <c r="E24" s="18">
+        <v>3450077830</v>
+      </c>
+      <c r="F24" s="55" t="s">
+        <v>133</v>
+      </c>
+      <c r="G24" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="H24" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="I24" s="26">
+        <v>45910</v>
+      </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="6"/>
       <c r="B25" s="8"/>
       <c r="C25" s="7"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="9"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="15"/>
       <c r="G25" s="6"/>
       <c r="H25" s="9"/>
+      <c r="I25" s="26"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="6"/>
@@ -4377,6 +4843,7 @@
       <c r="F26" s="9"/>
       <c r="G26" s="6"/>
       <c r="H26" s="9"/>
+      <c r="I26" s="26"/>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="6"/>
@@ -4658,27 +5125,17 @@
       <c r="G54" s="6"/>
       <c r="H54" s="9"/>
     </row>
-    <row r="55" spans="1:8">
-      <c r="A55" s="6"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="7"/>
-      <c r="D55" s="8"/>
-      <c r="E55" s="8"/>
-      <c r="F55" s="9"/>
-      <c r="G55" s="6"/>
-      <c r="H55" s="9"/>
-    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:C1">
-    <cfRule type="notContainsBlanks" priority="2">
+    <cfRule type="notContainsBlanks" priority="5">
       <formula>LEN(TRIM(B1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A18" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A2:A24" xr:uid="{69840FBE-03D6-48CB-B553-2E7186E1B4BD}">
       <formula1>$J$2</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G41" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G40" xr:uid="{AF5C7196-9DAE-4339-82D4-9412023E2B2A}">
       <formula1>"Vistoria Frustrada;,Vistoria Recusada,Bônus;,Desistência;,Inadimplência;,Política de Aceitação;,Duplicidade;,Demais Motivos,Falta de Vistoria;,"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6636,56 +7093,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10001</Type>
-    <SequenceNumber>1000</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10002</Type>
-    <SequenceNumber>1001</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10004</Type>
-    <SequenceNumber>1002</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-  <Receiver>
-    <Name>Document ID Generator</Name>
-    <Synchronization>Synchronous</Synchronization>
-    <Type>10006</Type>
-    <SequenceNumber>1003</SequenceNumber>
-    <Url/>
-    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
-    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
-    <Data/>
-    <Filter/>
-  </Receiver>
-</spe:Receivers>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010006E7B04763359F4AAB0FC84D5027BFC8" ma:contentTypeVersion="44" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ac14f8cb44178d381f4c0afb30680a90">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea" xmlns:ns3="ea6c6725-5210-4d6a-93cc-4cf85111ac5e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5e58414b065c9b590c40efa77cd84bb6" ns1:_="" ns2:_="" ns3:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7063,7 +7470,66 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<spe:Receivers xmlns:spe="http://schemas.microsoft.com/sharepoint/events">
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10001</Type>
+    <SequenceNumber>1000</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10002</Type>
+    <SequenceNumber>1001</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10004</Type>
+    <SequenceNumber>1002</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+  <Receiver>
+    <Name>Document ID Generator</Name>
+    <Synchronization>Synchronous</Synchronization>
+    <Type>10006</Type>
+    <SequenceNumber>1003</SequenceNumber>
+    <Url/>
+    <Assembly>Microsoft.Office.DocumentManagement, Version=16.0.0.0, Culture=neutral, PublicKeyToken=71e9bce111e9429c</Assembly>
+    <Class>Microsoft.Office.DocumentManagement.Internal.DocIdHandler</Class>
+    <Data/>
+    <Filter/>
+  </Receiver>
+</spe:Receivers>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_dlc_DocId xmlns="01f4fd7c-51c3-4ad2-ae58-e5034556b4ea">QAFFA7D2F2TC-2102087286-496579</_dlc_DocId>
@@ -7106,27 +7572,18 @@
 </p:properties>
 </file>
 
-<file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F01CFAB-0890-48C6-9F7B-BC4BA038F67A}"/>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{13279B2D-D76C-4CA7-B517-83259B9C0FB4}"/>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8F01CFAB-0890-48C6-9F7B-BC4BA038F67A}"/>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
 </file>
 
 <file path=customXml/itemProps4.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC9CB02D-0F63-4CE2-B316-61A87327416C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C48653D8-7562-408C-9B57-D83FFA71DB43}"/>
 </file>